--- a/www/terminologies/ASS-A33-AdministrativeGender-Sexe.xlsx
+++ b/www/terminologies/ASS-A33-AdministrativeGender-Sexe.xlsx
@@ -105,13 +105,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R249-Sexe/FHIR/TRE-R249-Sexe|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R249-Sexe/FHIR/TRE-R249-Sexe</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/administrative-gender|4.0.1</t>
+    <t>http://hl7.org/fhir/administrative-gender</t>
   </si>
   <si>
     <t>M</t>
